--- a/notes/个人学习计划2019 - 副本.xlsx
+++ b/notes/个人学习计划2019 - 副本.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\github\LangNote\notes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\langnote\notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475B936A-201C-4743-BE1B-63BEFBD0D6AA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40CB575-A74B-49B1-860A-D481D0141AC8}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5205" yWindow="1110" windowWidth="22485" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2017" sheetId="1" r:id="rId1"/>
-    <sheet name="2018" sheetId="2" r:id="rId2"/>
-    <sheet name="2019" sheetId="4" r:id="rId3"/>
-    <sheet name="上证50" sheetId="5" r:id="rId4"/>
-    <sheet name="2018年JavaEE课程大纲" sheetId="3" r:id="rId5"/>
-    <sheet name="CVS repo" sheetId="6" r:id="rId6"/>
+    <sheet name="2014" sheetId="9" r:id="rId1"/>
+    <sheet name="2015" sheetId="8" r:id="rId2"/>
+    <sheet name="2016" sheetId="7" r:id="rId3"/>
+    <sheet name="2017" sheetId="1" r:id="rId4"/>
+    <sheet name="2018" sheetId="2" r:id="rId5"/>
+    <sheet name="2019" sheetId="4" r:id="rId6"/>
+    <sheet name="上证50" sheetId="5" r:id="rId7"/>
+    <sheet name="2018年JavaEE课程大纲" sheetId="3" r:id="rId8"/>
+    <sheet name="CVS repo" sheetId="6" r:id="rId9"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -30,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1850" uniqueCount="1811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="1905">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3305,10 +3308,6 @@
   </si>
   <si>
     <t>洛阳钼业 (603993)</t>
-  </si>
-  <si>
-    <t>jdk juc包下所有类过了一遍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>java多线程实战手册第二章</t>
@@ -5393,10 +5392,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sed awk</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>github free 免费创建私有仓库</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5753,10 +5748,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Java原子类</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>游双《Linux高性能服务器编程》</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6520,10 +6511,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>到家</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Spring Boot 2精髓</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6588,10 +6575,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>到合肥</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>到深圳</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6601,6 +6584,346 @@
   </si>
   <si>
     <t>回上海</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20140131</t>
+  </si>
+  <si>
+    <t>20140130</t>
+  </si>
+  <si>
+    <t>20140129</t>
+  </si>
+  <si>
+    <t>20140128</t>
+  </si>
+  <si>
+    <t>20140127</t>
+  </si>
+  <si>
+    <t>20140126</t>
+  </si>
+  <si>
+    <t>20140125</t>
+  </si>
+  <si>
+    <t>20140124</t>
+  </si>
+  <si>
+    <t>20140123</t>
+  </si>
+  <si>
+    <t>20140122</t>
+  </si>
+  <si>
+    <t>20140121</t>
+  </si>
+  <si>
+    <t>20140120</t>
+  </si>
+  <si>
+    <t>20140119</t>
+  </si>
+  <si>
+    <t>20140118</t>
+  </si>
+  <si>
+    <t>20140117</t>
+  </si>
+  <si>
+    <t>20140116</t>
+  </si>
+  <si>
+    <t>20140115</t>
+  </si>
+  <si>
+    <t>20140114</t>
+  </si>
+  <si>
+    <t>20140113</t>
+  </si>
+  <si>
+    <t>20140112</t>
+  </si>
+  <si>
+    <t>20140111</t>
+  </si>
+  <si>
+    <t>20140110</t>
+  </si>
+  <si>
+    <t>20140109</t>
+  </si>
+  <si>
+    <t>20140108</t>
+  </si>
+  <si>
+    <t>20140107</t>
+  </si>
+  <si>
+    <t>20140106</t>
+  </si>
+  <si>
+    <t>20140105</t>
+  </si>
+  <si>
+    <t>20140104</t>
+  </si>
+  <si>
+    <t>20140103</t>
+  </si>
+  <si>
+    <t>20140102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20140101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>201402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>201403</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>201404</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>201405</t>
+  </si>
+  <si>
+    <t>201406</t>
+  </si>
+  <si>
+    <t>201407</t>
+  </si>
+  <si>
+    <t>201408</t>
+  </si>
+  <si>
+    <t>201409</t>
+  </si>
+  <si>
+    <t>201410</t>
+  </si>
+  <si>
+    <t>201411</t>
+  </si>
+  <si>
+    <t>201412</t>
+  </si>
+  <si>
+    <t>201501</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>201502</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>201503</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>201504</t>
+  </si>
+  <si>
+    <t>201505</t>
+  </si>
+  <si>
+    <t>201506</t>
+  </si>
+  <si>
+    <t>201507</t>
+  </si>
+  <si>
+    <t>201508</t>
+  </si>
+  <si>
+    <t>201509</t>
+  </si>
+  <si>
+    <t>201510</t>
+  </si>
+  <si>
+    <t>201511</t>
+  </si>
+  <si>
+    <t>201512</t>
+  </si>
+  <si>
+    <t>201603</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>201602</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>201601</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>201604</t>
+  </si>
+  <si>
+    <t>201605</t>
+  </si>
+  <si>
+    <t>201606</t>
+  </si>
+  <si>
+    <t>201607</t>
+  </si>
+  <si>
+    <t>201608</t>
+  </si>
+  <si>
+    <t>201609</t>
+  </si>
+  <si>
+    <t>201610</t>
+  </si>
+  <si>
+    <t>201611</t>
+  </si>
+  <si>
+    <t>201612</t>
+  </si>
+  <si>
+    <t>8月培训 在合肥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10月去武汉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圣诞节在合肥 科大讯飞面试 传智播客入学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大年初一</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2月18除夕 武汉 一个人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>深圳 龙岗 布吉-地铁站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2017年搬出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>智莱科技 塘朗新村</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>离职智莱科技，人生一大失误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>气死</t>
+  </si>
+  <si>
+    <t>南山智园c3</t>
+  </si>
+  <si>
+    <t>十九大常委名单</t>
+  </si>
+  <si>
+    <t>在北京</t>
+  </si>
+  <si>
+    <t>陪父母到合肥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>南山图书馆附近
+前海金岸金丰阁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>深圳市金和盛软件 
+深圳市南山区数字文化产业基地东塔704</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>荔香公园</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>筹备买房</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>房价没涨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新安卓同事入职 周航</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>买包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>买iPhone，买mac</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sed awk grep</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jdk juc包下所有类过了一遍 AQS UnSafe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Java原子类
+Atomic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在开源项目那么多，用哪个？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3月出考研成绩 合肥邮电学院 电信面试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6月离校 在合肥 马鞍山路 家乐福</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>学习Java EE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安全卫士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>影音播放器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>除夕 早上到家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2月7日除夕</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6608,7 +6931,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6751,8 +7074,16 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6762,6 +7093,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7015,7 +7352,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7135,6 +7472,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7416,6 +7756,439 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4E33173-997F-4553-8EFA-63F55CE6EBBA}">
+  <dimension ref="A1:B42"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="1" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="1" t="s">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="1" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="1" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="1" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="1" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="1" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="1" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="1" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="1" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="1" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="1" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="1" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="1" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="1" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="1" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="1" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B30" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="1" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="1" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="1" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="1" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="1" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="1" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="1" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="1" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="1" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="1" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="1" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="1" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8298A7F1-C2F5-49AA-98EA-50390782F5B3}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="2" width="24.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>1852</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="40.5">
+      <c r="A6" s="1" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="27">
+      <c r="A8" s="1" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C5250C6-1281-4939-80EE-E0EAA9B95551}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="2" width="21.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G366"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -7438,258 +8211,258 @@
     </row>
     <row r="2" spans="1:2" ht="24.6" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="27">
       <c r="A19" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>1035</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>1036</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>1037</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B20" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C20" t="s">
         <v>1039</v>
       </c>
-      <c r="C20" t="s">
-        <v>1040</v>
-      </c>
       <c r="D20" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="E20" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B21" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C21" t="s">
         <v>1041</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>1042</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B22" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B23" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C23" t="s">
-        <v>1646</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B24" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C24" t="s">
         <v>1046</v>
       </c>
-      <c r="C24" t="s">
-        <v>1047</v>
-      </c>
       <c r="D24" t="s">
-        <v>1647</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="11.45" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="11.45" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1790</v>
+        <v>1029</v>
+      </c>
+      <c r="B28" s="40" t="s">
+        <v>1903</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="11.45" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B29" t="s">
-        <v>1789</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="11.45" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="11.45" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="11.45" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B33" t="s">
-        <v>1803</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="1" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="1" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B39" t="s">
         <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>1648</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -7703,10 +8476,10 @@
         <v>5</v>
       </c>
       <c r="D40" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
       <c r="E40" t="s">
-        <v>1650</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -7740,10 +8513,10 @@
         <v>12</v>
       </c>
       <c r="E45" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F45" s="2" t="s">
         <v>1048</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -7759,13 +8532,13 @@
         <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>1651</v>
+        <v>1648</v>
       </c>
       <c r="C47" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
       <c r="D47" t="s">
-        <v>1653</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -7776,7 +8549,7 @@
         <v>16</v>
       </c>
       <c r="C48" t="s">
-        <v>1654</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -7793,7 +8566,7 @@
         <v>21</v>
       </c>
       <c r="E49" t="s">
-        <v>1655</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -7820,7 +8593,7 @@
         <v>32</v>
       </c>
       <c r="D52" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -7828,7 +8601,7 @@
         <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -7919,10 +8692,10 @@
         <v>49</v>
       </c>
       <c r="C64" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="D64" t="s">
-        <v>1656</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -7960,7 +8733,7 @@
         <v>59</v>
       </c>
       <c r="B68" t="s">
-        <v>1657</v>
+        <v>1654</v>
       </c>
       <c r="C68" t="s">
         <v>60</v>
@@ -8016,7 +8789,7 @@
         <v>75</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -8032,7 +8805,7 @@
         <v>78</v>
       </c>
       <c r="B74" t="s">
-        <v>1658</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -8071,7 +8844,7 @@
         <v>88</v>
       </c>
       <c r="B77" t="s">
-        <v>1640</v>
+        <v>1637</v>
       </c>
       <c r="C77" t="s">
         <v>93</v>
@@ -8099,7 +8872,7 @@
         <v>94</v>
       </c>
       <c r="C79" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -8126,10 +8899,10 @@
         <v>104</v>
       </c>
       <c r="C82" t="s">
-        <v>1642</v>
+        <v>1639</v>
       </c>
       <c r="D82" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -8152,10 +8925,10 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
       <c r="C86" t="s">
-        <v>1660</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -8247,7 +9020,7 @@
         <v>123</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -8286,7 +9059,7 @@
         <v>129</v>
       </c>
       <c r="B108" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -8381,19 +9154,22 @@
         <v>152</v>
       </c>
       <c r="D121" t="s">
+        <v>993</v>
+      </c>
+      <c r="E121" t="s">
         <v>994</v>
       </c>
-      <c r="E121" t="s">
+      <c r="F121" s="2" t="s">
         <v>995</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="1" t="s">
         <v>153</v>
       </c>
+      <c r="B122" t="s">
+        <v>1880</v>
+      </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="1" t="s">
@@ -8410,7 +9186,7 @@
         <v>156</v>
       </c>
       <c r="B125" t="s">
-        <v>1804</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -8428,7 +9204,7 @@
         <v>159</v>
       </c>
       <c r="B128" t="s">
-        <v>1805</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -8441,7 +9217,7 @@
         <v>161</v>
       </c>
       <c r="B130" t="s">
-        <v>1803</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -8538,7 +9314,7 @@
         <v>178</v>
       </c>
       <c r="B147" t="s">
-        <v>1786</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -9046,630 +9822,765 @@
     </row>
     <row r="245" spans="1:2">
       <c r="A245" s="1" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" s="1" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="247" spans="1:2">
       <c r="A247" s="1" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="248" spans="1:2">
       <c r="A248" s="1" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" s="1" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" s="1" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" s="1" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="252" spans="1:2">
       <c r="A252" s="1" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="B252" t="s">
-        <v>1785</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" s="1" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="B253" t="s">
-        <v>1786</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="254" spans="1:2">
       <c r="A254" s="1" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="B254" t="s">
-        <v>1787</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" s="1" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="B255" t="s">
-        <v>1788</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" s="1" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="1" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="1" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B258" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="1" t="s">
         <v>1673</v>
       </c>
-    </row>
-    <row r="257" spans="1:1">
-      <c r="A257" s="1" t="s">
+      <c r="B259" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="1" t="s">
         <v>1674</v>
       </c>
     </row>
-    <row r="258" spans="1:1">
-      <c r="A258" s="1" t="s">
+    <row r="261" spans="1:2">
+      <c r="A261" s="1" t="s">
         <v>1675</v>
       </c>
     </row>
-    <row r="259" spans="1:1">
-      <c r="A259" s="1" t="s">
+    <row r="262" spans="1:2">
+      <c r="A262" s="1" t="s">
         <v>1676</v>
       </c>
     </row>
-    <row r="260" spans="1:1">
-      <c r="A260" s="1" t="s">
+    <row r="263" spans="1:2">
+      <c r="A263" s="1" t="s">
         <v>1677</v>
       </c>
     </row>
-    <row r="261" spans="1:1">
-      <c r="A261" s="1" t="s">
+    <row r="264" spans="1:2">
+      <c r="A264" s="1" t="s">
         <v>1678</v>
       </c>
     </row>
-    <row r="262" spans="1:1">
-      <c r="A262" s="1" t="s">
+    <row r="265" spans="1:2">
+      <c r="A265" s="1" t="s">
         <v>1679</v>
       </c>
     </row>
-    <row r="263" spans="1:1">
-      <c r="A263" s="1" t="s">
+    <row r="266" spans="1:2">
+      <c r="A266" s="1" t="s">
         <v>1680</v>
       </c>
     </row>
-    <row r="264" spans="1:1">
-      <c r="A264" s="1" t="s">
+    <row r="267" spans="1:2">
+      <c r="A267" s="1" t="s">
         <v>1681</v>
       </c>
     </row>
-    <row r="265" spans="1:1">
-      <c r="A265" s="1" t="s">
+    <row r="268" spans="1:2">
+      <c r="A268" s="1" t="s">
         <v>1682</v>
       </c>
     </row>
-    <row r="266" spans="1:1">
-      <c r="A266" s="1" t="s">
+    <row r="269" spans="1:2">
+      <c r="A269" s="1" t="s">
         <v>1683</v>
       </c>
     </row>
-    <row r="267" spans="1:1">
-      <c r="A267" s="1" t="s">
+    <row r="270" spans="1:2">
+      <c r="A270" s="1" t="s">
         <v>1684</v>
       </c>
     </row>
-    <row r="268" spans="1:1">
-      <c r="A268" s="1" t="s">
+    <row r="271" spans="1:2">
+      <c r="A271" s="1" t="s">
         <v>1685</v>
       </c>
     </row>
-    <row r="269" spans="1:1">
-      <c r="A269" s="1" t="s">
+    <row r="272" spans="1:2">
+      <c r="A272" s="1" t="s">
         <v>1686</v>
-      </c>
-    </row>
-    <row r="270" spans="1:1">
-      <c r="A270" s="1" t="s">
-        <v>1687</v>
-      </c>
-    </row>
-    <row r="271" spans="1:1">
-      <c r="A271" s="1" t="s">
-        <v>1688</v>
-      </c>
-    </row>
-    <row r="272" spans="1:1">
-      <c r="A272" s="1" t="s">
-        <v>1689</v>
       </c>
     </row>
     <row r="273" spans="1:1">
       <c r="A273" s="1" t="s">
-        <v>1690</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="274" spans="1:1">
       <c r="A274" s="1" t="s">
-        <v>1691</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="275" spans="1:1">
       <c r="A275" s="1" t="s">
-        <v>1692</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="276" spans="1:1">
       <c r="A276" s="1" t="s">
-        <v>1693</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="277" spans="1:1">
       <c r="A277" s="1" t="s">
-        <v>1694</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="278" spans="1:1">
       <c r="A278" s="1" t="s">
-        <v>1695</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="279" spans="1:1">
       <c r="A279" s="1" t="s">
-        <v>1696</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280" s="1" t="s">
-        <v>1697</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281" s="1" t="s">
-        <v>1698</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="282" spans="1:1">
       <c r="A282" s="1" t="s">
-        <v>1699</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" s="1" t="s">
-        <v>1700</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" s="1" t="s">
-        <v>1701</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="285" spans="1:1">
       <c r="A285" s="1" t="s">
-        <v>1702</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="286" spans="1:1">
       <c r="A286" s="1" t="s">
-        <v>1703</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="287" spans="1:1">
       <c r="A287" s="1" t="s">
-        <v>1704</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" s="1" t="s">
-        <v>1705</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="1" t="s">
-        <v>1706</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="290" spans="1:2">
       <c r="A290" s="1" t="s">
-        <v>1707</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="291" spans="1:2">
       <c r="A291" s="1" t="s">
-        <v>1708</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" s="1" t="s">
-        <v>1709</v>
+        <v>1706</v>
       </c>
       <c r="B292" t="s">
-        <v>1784</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="293" spans="1:2">
       <c r="A293" s="1" t="s">
-        <v>1710</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="294" spans="1:2">
       <c r="A294" s="1" t="s">
-        <v>1711</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="295" spans="1:2">
       <c r="A295" s="1" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="296" spans="1:2">
       <c r="A296" s="1" t="s">
-        <v>1713</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" s="1" t="s">
-        <v>1714</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" s="1" t="s">
-        <v>1715</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" s="1" t="s">
-        <v>1716</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="300" spans="1:2">
       <c r="A300" s="1" t="s">
-        <v>1717</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="301" spans="1:2">
       <c r="A301" s="1" t="s">
-        <v>1718</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="302" spans="1:2">
       <c r="A302" s="1" t="s">
-        <v>1719</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" s="1" t="s">
-        <v>1720</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="304" spans="1:2">
       <c r="A304" s="1" t="s">
-        <v>1721</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="305" spans="1:1">
       <c r="A305" s="1" t="s">
-        <v>1722</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="306" spans="1:1">
       <c r="A306" s="1" t="s">
-        <v>1723</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="307" spans="1:1">
       <c r="A307" s="1" t="s">
-        <v>1724</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="308" spans="1:1">
       <c r="A308" s="1" t="s">
-        <v>1725</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="309" spans="1:1">
       <c r="A309" s="1" t="s">
-        <v>1726</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="310" spans="1:1">
       <c r="A310" s="1" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="311" spans="1:1">
       <c r="A311" s="1" t="s">
-        <v>1728</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="312" spans="1:1">
       <c r="A312" s="1" t="s">
-        <v>1729</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="313" spans="1:1">
       <c r="A313" s="1" t="s">
-        <v>1730</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="314" spans="1:1">
       <c r="A314" s="1" t="s">
-        <v>1731</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="315" spans="1:1">
       <c r="A315" s="1" t="s">
-        <v>1732</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="316" spans="1:1">
       <c r="A316" s="1" t="s">
-        <v>1733</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="317" spans="1:1">
       <c r="A317" s="1" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="318" spans="1:1">
       <c r="A318" s="1" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="319" spans="1:1">
       <c r="A319" s="1" t="s">
-        <v>1736</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="320" spans="1:1">
       <c r="A320" s="1" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321" s="1" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322" s="1" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323" s="1" t="s">
         <v>1737</v>
       </c>
-    </row>
-    <row r="321" spans="1:2">
-      <c r="A321" s="1" t="s">
+      <c r="B323" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C323" t="s">
+        <v>1882</v>
+      </c>
+      <c r="D323" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324" s="1" t="s">
         <v>1738</v>
       </c>
     </row>
-    <row r="322" spans="1:2">
-      <c r="A322" s="1" t="s">
+    <row r="325" spans="1:4">
+      <c r="A325" s="1" t="s">
         <v>1739</v>
       </c>
-    </row>
-    <row r="323" spans="1:2">
-      <c r="A323" s="1" t="s">
+      <c r="B325" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
+      <c r="A326" s="1" t="s">
         <v>1740</v>
       </c>
     </row>
-    <row r="324" spans="1:2">
-      <c r="A324" s="1" t="s">
+    <row r="327" spans="1:4">
+      <c r="A327" s="1" t="s">
         <v>1741</v>
       </c>
-    </row>
-    <row r="325" spans="1:2">
-      <c r="A325" s="1" t="s">
+      <c r="B327" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
+      <c r="A328" s="1" t="s">
         <v>1742</v>
       </c>
-      <c r="B325" t="s">
-        <v>1806</v>
-      </c>
-    </row>
-    <row r="326" spans="1:2">
-      <c r="A326" s="1" t="s">
+      <c r="B328" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
+      <c r="A329" s="1" t="s">
         <v>1743</v>
       </c>
-    </row>
-    <row r="327" spans="1:2">
-      <c r="A327" s="1" t="s">
+      <c r="B329" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
+      <c r="A330" s="1" t="s">
         <v>1744</v>
       </c>
-    </row>
-    <row r="328" spans="1:2">
-      <c r="A328" s="1" t="s">
+      <c r="B330" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
+      <c r="A331" s="1" t="s">
         <v>1745</v>
       </c>
-    </row>
-    <row r="329" spans="1:2">
-      <c r="A329" s="1" t="s">
+      <c r="B331" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
+      <c r="A332" s="1" t="s">
         <v>1746</v>
       </c>
-    </row>
-    <row r="330" spans="1:2">
-      <c r="A330" s="1" t="s">
+      <c r="B332" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
+      <c r="A333" s="1" t="s">
         <v>1747</v>
       </c>
-    </row>
-    <row r="331" spans="1:2">
-      <c r="A331" s="1" t="s">
+      <c r="B333" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
+      <c r="A334" s="1" t="s">
         <v>1748</v>
       </c>
-    </row>
-    <row r="332" spans="1:2">
-      <c r="A332" s="1" t="s">
+      <c r="B334" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
+      <c r="A335" s="1" t="s">
         <v>1749</v>
       </c>
-    </row>
-    <row r="333" spans="1:2">
-      <c r="A333" s="1" t="s">
+      <c r="B335" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
+      <c r="A336" s="1" t="s">
         <v>1750</v>
       </c>
-    </row>
-    <row r="334" spans="1:2">
-      <c r="A334" s="1" t="s">
+      <c r="B336" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="1" t="s">
         <v>1751</v>
       </c>
-    </row>
-    <row r="335" spans="1:2">
-      <c r="A335" s="1" t="s">
+      <c r="B337" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="1" t="s">
         <v>1752</v>
       </c>
-    </row>
-    <row r="336" spans="1:2">
-      <c r="A336" s="1" t="s">
+      <c r="B338" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="1" t="s">
         <v>1753</v>
       </c>
-    </row>
-    <row r="337" spans="1:1">
-      <c r="A337" s="1" t="s">
+      <c r="B339" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="1" t="s">
         <v>1754</v>
       </c>
-    </row>
-    <row r="338" spans="1:1">
-      <c r="A338" s="1" t="s">
+      <c r="B340" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="1" t="s">
         <v>1755</v>
       </c>
-    </row>
-    <row r="339" spans="1:1">
-      <c r="A339" s="1" t="s">
+      <c r="B341" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" s="1" t="s">
         <v>1756</v>
       </c>
-    </row>
-    <row r="340" spans="1:1">
-      <c r="A340" s="1" t="s">
+      <c r="B342" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="1" t="s">
         <v>1757</v>
       </c>
-    </row>
-    <row r="341" spans="1:1">
-      <c r="A341" s="1" t="s">
+      <c r="B343" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="1" t="s">
         <v>1758</v>
       </c>
-    </row>
-    <row r="342" spans="1:1">
-      <c r="A342" s="1" t="s">
+      <c r="B344" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" s="1" t="s">
         <v>1759</v>
       </c>
-    </row>
-    <row r="343" spans="1:1">
-      <c r="A343" s="1" t="s">
+      <c r="B345" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="1" t="s">
         <v>1760</v>
       </c>
-    </row>
-    <row r="344" spans="1:1">
-      <c r="A344" s="1" t="s">
+      <c r="B346" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="1" t="s">
         <v>1761</v>
       </c>
-    </row>
-    <row r="345" spans="1:1">
-      <c r="A345" s="1" t="s">
+      <c r="B347" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="1" t="s">
         <v>1762</v>
       </c>
-    </row>
-    <row r="346" spans="1:1">
-      <c r="A346" s="1" t="s">
+      <c r="B348" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="1" t="s">
         <v>1763</v>
       </c>
-    </row>
-    <row r="347" spans="1:1">
-      <c r="A347" s="1" t="s">
+      <c r="B349" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="1" t="s">
         <v>1764</v>
       </c>
-    </row>
-    <row r="348" spans="1:1">
-      <c r="A348" s="1" t="s">
+      <c r="B350" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="1" t="s">
         <v>1765</v>
       </c>
-    </row>
-    <row r="349" spans="1:1">
-      <c r="A349" s="1" t="s">
+      <c r="B351" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" s="1" t="s">
         <v>1766</v>
       </c>
-    </row>
-    <row r="350" spans="1:1">
-      <c r="A350" s="1" t="s">
+      <c r="B352" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="1" t="s">
         <v>1767</v>
       </c>
-    </row>
-    <row r="351" spans="1:1">
-      <c r="A351" s="1" t="s">
+      <c r="B353" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="1" t="s">
         <v>1768</v>
       </c>
-    </row>
-    <row r="352" spans="1:1">
-      <c r="A352" s="1" t="s">
+      <c r="B354" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="1" t="s">
         <v>1769</v>
       </c>
-    </row>
-    <row r="353" spans="1:1">
-      <c r="A353" s="1" t="s">
+      <c r="B355" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="1" t="s">
         <v>1770</v>
       </c>
-    </row>
-    <row r="354" spans="1:1">
-      <c r="A354" s="1" t="s">
+      <c r="B356" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" s="1" t="s">
         <v>1771</v>
       </c>
-    </row>
-    <row r="355" spans="1:1">
-      <c r="A355" s="1" t="s">
+      <c r="B357" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="1" t="s">
         <v>1772</v>
       </c>
-    </row>
-    <row r="356" spans="1:1">
-      <c r="A356" s="1" t="s">
+      <c r="B358" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="1" t="s">
         <v>1773</v>
       </c>
-    </row>
-    <row r="357" spans="1:1">
-      <c r="A357" s="1" t="s">
+      <c r="B359" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="1" t="s">
         <v>1774</v>
       </c>
-    </row>
-    <row r="358" spans="1:1">
-      <c r="A358" s="1" t="s">
+      <c r="B360" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="1" t="s">
         <v>1775</v>
       </c>
-    </row>
-    <row r="359" spans="1:1">
-      <c r="A359" s="1" t="s">
+      <c r="B361" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="1" t="s">
         <v>1776</v>
       </c>
-    </row>
-    <row r="360" spans="1:1">
-      <c r="A360" s="1" t="s">
+      <c r="B362" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="1" t="s">
         <v>1777</v>
       </c>
-    </row>
-    <row r="361" spans="1:1">
-      <c r="A361" s="1" t="s">
+      <c r="B363" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="1" t="s">
         <v>1778</v>
       </c>
-    </row>
-    <row r="362" spans="1:1">
-      <c r="A362" s="1" t="s">
+      <c r="B364" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="1" t="s">
         <v>1779</v>
       </c>
-    </row>
-    <row r="363" spans="1:1">
-      <c r="A363" s="1" t="s">
+      <c r="B365" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="1" t="s">
         <v>1780</v>
       </c>
-    </row>
-    <row r="364" spans="1:1">
-      <c r="A364" s="1" t="s">
-        <v>1781</v>
-      </c>
-    </row>
-    <row r="365" spans="1:1">
-      <c r="A365" s="1" t="s">
-        <v>1782</v>
-      </c>
-    </row>
-    <row r="366" spans="1:1">
-      <c r="A366" s="1" t="s">
-        <v>1783</v>
+      <c r="B366" t="s">
+        <v>1884</v>
       </c>
     </row>
   </sheetData>
@@ -9679,7 +10590,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L368"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -9710,7 +10621,7 @@
         <v>857</v>
       </c>
       <c r="B3" t="s">
-        <v>1793</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9718,7 +10629,7 @@
         <v>858</v>
       </c>
       <c r="B4" t="s">
-        <v>1794</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9726,7 +10637,7 @@
         <v>859</v>
       </c>
       <c r="B5" t="s">
-        <v>1795</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -9799,7 +10710,7 @@
         <v>873</v>
       </c>
       <c r="B19" t="s">
-        <v>1792</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -10053,7 +10964,7 @@
         <v>686</v>
       </c>
       <c r="B68" t="s">
-        <v>1807</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -10061,7 +10972,7 @@
         <v>687</v>
       </c>
       <c r="B69" t="s">
-        <v>1808</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -10119,7 +11030,7 @@
         <v>698</v>
       </c>
       <c r="B80" t="s">
-        <v>1796</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -10127,7 +11038,7 @@
         <v>699</v>
       </c>
       <c r="B81" t="s">
-        <v>1797</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -10175,13 +11086,13 @@
         <v>222</v>
       </c>
       <c r="B90" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C90" t="s">
         <v>254</v>
       </c>
       <c r="D90" t="s">
-        <v>1791</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -10192,7 +11103,7 @@
         <v>256</v>
       </c>
       <c r="C91" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -10233,10 +11144,10 @@
         <v>231</v>
       </c>
       <c r="B98" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C98" t="s">
         <v>1453</v>
-      </c>
-      <c r="C98" t="s">
-        <v>1454</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -10267,7 +11178,7 @@
         <v>261</v>
       </c>
       <c r="G100" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -10281,7 +11192,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -10292,10 +11203,10 @@
         <v>265</v>
       </c>
       <c r="C102" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D102" t="s">
         <v>1449</v>
-      </c>
-      <c r="D102" t="s">
-        <v>1450</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -10306,7 +11217,7 @@
         <v>268</v>
       </c>
       <c r="C103" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="40.5">
@@ -10343,33 +11254,33 @@
         <v>238</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="81">
+    <row r="106" spans="1:9" ht="40.5">
       <c r="A106" s="1" t="s">
         <v>239</v>
       </c>
       <c r="B106" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C106" t="s">
         <v>1051</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
         <v>1052</v>
       </c>
-      <c r="D106" t="s">
-        <v>1053</v>
-      </c>
       <c r="E106" t="s">
+        <v>1442</v>
+      </c>
+      <c r="F106" t="s">
         <v>1443</v>
       </c>
-      <c r="F106" t="s">
+      <c r="G106" t="s">
         <v>1444</v>
       </c>
-      <c r="G106" t="s">
+      <c r="H106" s="2" t="s">
         <v>1445</v>
       </c>
-      <c r="H106" s="2" t="s">
+      <c r="I106" s="2" t="s">
         <v>1446</v>
-      </c>
-      <c r="I106" s="2" t="s">
-        <v>1447</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -10380,7 +11291,7 @@
         <v>274</v>
       </c>
       <c r="C107" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -10394,7 +11305,7 @@
         <v>278</v>
       </c>
       <c r="D108" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -10407,16 +11318,16 @@
         <v>241</v>
       </c>
       <c r="B110" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D110" t="s">
         <v>1055</v>
-      </c>
-      <c r="D110" t="s">
-        <v>1056</v>
       </c>
       <c r="E110" t="s">
         <v>276</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -10427,7 +11338,7 @@
         <v>279</v>
       </c>
       <c r="C111" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -10440,13 +11351,13 @@
         <v>243</v>
       </c>
       <c r="B113" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C113" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D113" t="s">
         <v>1439</v>
-      </c>
-      <c r="D113" t="s">
-        <v>1440</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -10454,7 +11365,7 @@
         <v>244</v>
       </c>
       <c r="B114" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -10462,7 +11373,7 @@
         <v>245</v>
       </c>
       <c r="B115" t="s">
-        <v>1798</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="94.5">
@@ -10476,19 +11387,19 @@
         <v>281</v>
       </c>
       <c r="D116" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E116" t="s">
         <v>1061</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" s="2" t="s">
         <v>1062</v>
       </c>
-      <c r="F116" s="2" t="s">
+      <c r="G116" s="2" t="s">
         <v>1063</v>
       </c>
-      <c r="G116" s="2" t="s">
+      <c r="H116" t="s">
         <v>1064</v>
-      </c>
-      <c r="H116" t="s">
-        <v>1065</v>
       </c>
       <c r="I116" s="4" t="s">
         <v>282</v>
@@ -10499,16 +11410,16 @@
         <v>247</v>
       </c>
       <c r="B117" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C117" s="2" t="s">
         <v>1066</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>1067</v>
       </c>
       <c r="D117" t="s">
         <v>283</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -10516,10 +11427,10 @@
         <v>248</v>
       </c>
       <c r="B118" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C118" t="s">
         <v>1069</v>
-      </c>
-      <c r="C118" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -10527,10 +11438,10 @@
         <v>249</v>
       </c>
       <c r="B119" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C119" t="s">
         <v>1071</v>
-      </c>
-      <c r="C119" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="27">
@@ -10538,7 +11449,7 @@
         <v>250</v>
       </c>
       <c r="B120" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>284</v>
@@ -10549,7 +11460,7 @@
         <v>251</v>
       </c>
       <c r="B121" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="C121" t="s">
         <v>285</v>
@@ -10560,10 +11471,10 @@
         <v>252</v>
       </c>
       <c r="B122" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C122" s="2" t="s">
         <v>1075</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="27">
@@ -10571,7 +11482,7 @@
         <v>253</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="54">
@@ -10582,10 +11493,10 @@
         <v>316</v>
       </c>
       <c r="C124" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D124" t="s">
         <v>1078</v>
-      </c>
-      <c r="D124" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -10593,16 +11504,16 @@
         <v>287</v>
       </c>
       <c r="B125" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C125" t="s">
         <v>1080</v>
       </c>
-      <c r="C125" t="s">
+      <c r="D125" t="s">
         <v>1081</v>
       </c>
-      <c r="D125" t="s">
+      <c r="E125" t="s">
         <v>1082</v>
-      </c>
-      <c r="E125" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -10610,10 +11521,10 @@
         <v>288</v>
       </c>
       <c r="B126" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C126" t="s">
         <v>1084</v>
-      </c>
-      <c r="C126" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -10621,10 +11532,10 @@
         <v>289</v>
       </c>
       <c r="B127" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C127" t="s">
         <v>1086</v>
-      </c>
-      <c r="C127" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -10638,7 +11549,7 @@
         <v>317</v>
       </c>
       <c r="D128" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -10646,13 +11557,13 @@
         <v>291</v>
       </c>
       <c r="B129" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C129" t="s">
         <v>1089</v>
       </c>
-      <c r="C129" t="s">
+      <c r="D129" t="s">
         <v>1090</v>
-      </c>
-      <c r="D129" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="27">
@@ -10669,10 +11580,10 @@
         <v>321</v>
       </c>
       <c r="E130" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F130" t="s">
         <v>1092</v>
-      </c>
-      <c r="F130" t="s">
-        <v>1093</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -10683,16 +11594,16 @@
         <v>322</v>
       </c>
       <c r="C131" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D131" t="s">
         <v>1094</v>
       </c>
-      <c r="D131" t="s">
+      <c r="E131" t="s">
         <v>1095</v>
       </c>
-      <c r="E131" t="s">
+      <c r="F131" t="s">
         <v>1096</v>
-      </c>
-      <c r="F131" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -10700,13 +11611,13 @@
         <v>294</v>
       </c>
       <c r="B132" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C132" t="s">
         <v>1098</v>
       </c>
-      <c r="C132" t="s">
+      <c r="D132" t="s">
         <v>1099</v>
-      </c>
-      <c r="D132" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -10714,7 +11625,7 @@
         <v>295</v>
       </c>
       <c r="B133" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C133" t="s">
         <v>323</v>
@@ -10725,7 +11636,7 @@
         <v>296</v>
       </c>
       <c r="B134" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="27">
@@ -10733,7 +11644,7 @@
         <v>297</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -10741,7 +11652,7 @@
         <v>298</v>
       </c>
       <c r="B136" t="s">
-        <v>1799</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -10749,13 +11660,13 @@
         <v>299</v>
       </c>
       <c r="B137" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C137" t="s">
         <v>324</v>
       </c>
       <c r="D137" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="27">
@@ -10763,16 +11674,16 @@
         <v>300</v>
       </c>
       <c r="B138" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C138" t="s">
         <v>1106</v>
       </c>
-      <c r="C138" t="s">
+      <c r="D138" t="s">
         <v>1107</v>
       </c>
-      <c r="D138" t="s">
-        <v>1108</v>
-      </c>
       <c r="E138" s="5" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -10780,7 +11691,7 @@
         <v>301</v>
       </c>
       <c r="B139" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -10791,13 +11702,13 @@
         <v>325</v>
       </c>
       <c r="C140" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D140" t="s">
         <v>1110</v>
       </c>
-      <c r="D140" t="s">
+      <c r="E140" t="s">
         <v>1111</v>
-      </c>
-      <c r="E140" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -10810,13 +11721,13 @@
         <v>304</v>
       </c>
       <c r="B142" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C142" t="s">
         <v>1113</v>
       </c>
-      <c r="C142" t="s">
-        <v>1114</v>
-      </c>
       <c r="D142" t="s">
-        <v>1800</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -10824,7 +11735,7 @@
         <v>305</v>
       </c>
       <c r="B143" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -10832,7 +11743,7 @@
         <v>306</v>
       </c>
       <c r="B144" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -10840,13 +11751,13 @@
         <v>307</v>
       </c>
       <c r="B145" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C145" t="s">
         <v>326</v>
       </c>
       <c r="D145" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -10854,10 +11765,10 @@
         <v>308</v>
       </c>
       <c r="B146" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C146" t="s">
         <v>1118</v>
-      </c>
-      <c r="C146" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="15">
@@ -10865,13 +11776,13 @@
         <v>309</v>
       </c>
       <c r="B147" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C147" t="s">
         <v>1120</v>
       </c>
-      <c r="C147" t="s">
+      <c r="D147" t="s">
         <v>1121</v>
-      </c>
-      <c r="D147" t="s">
-        <v>1122</v>
       </c>
       <c r="E147" t="s">
         <v>327</v>
@@ -10882,10 +11793,10 @@
         <v>310</v>
       </c>
       <c r="B148" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C148" t="s">
         <v>1123</v>
-      </c>
-      <c r="C148" t="s">
-        <v>1124</v>
       </c>
       <c r="D148" t="s">
         <v>328</v>
@@ -10899,10 +11810,10 @@
         <v>329</v>
       </c>
       <c r="C149" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D149" t="s">
         <v>1125</v>
-      </c>
-      <c r="D149" t="s">
-        <v>1126</v>
       </c>
       <c r="E149" t="s">
         <v>330</v>
@@ -10918,13 +11829,13 @@
         <v>313</v>
       </c>
       <c r="B151" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C151" s="2" t="s">
         <v>1127</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="D151" t="s">
         <v>1128</v>
-      </c>
-      <c r="D151" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -10940,10 +11851,10 @@
         <v>315</v>
       </c>
       <c r="B153" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>1130</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -10951,7 +11862,7 @@
         <v>331</v>
       </c>
       <c r="B154" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -10964,7 +11875,7 @@
         <v>332</v>
       </c>
       <c r="B156" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -10985,10 +11896,10 @@
         <v>335</v>
       </c>
       <c r="B159" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C159" t="s">
         <v>1134</v>
-      </c>
-      <c r="C159" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -10996,10 +11907,10 @@
         <v>336</v>
       </c>
       <c r="B160" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C160" t="s">
         <v>1136</v>
-      </c>
-      <c r="C160" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -11012,10 +11923,10 @@
         <v>338</v>
       </c>
       <c r="B162" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C162" s="2" t="s">
         <v>1138</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -11026,7 +11937,7 @@
         <v>678</v>
       </c>
       <c r="C163" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -11034,7 +11945,7 @@
         <v>340</v>
       </c>
       <c r="B164" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="C164" t="s">
         <v>364</v>
@@ -11048,16 +11959,16 @@
         <v>366</v>
       </c>
       <c r="C165" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="D165" t="s">
         <v>365</v>
       </c>
       <c r="E165" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F165" s="2" t="s">
         <v>1143</v>
-      </c>
-      <c r="F165" s="2" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="54">
@@ -11065,25 +11976,25 @@
         <v>342</v>
       </c>
       <c r="B166" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C166" t="s">
         <v>1145</v>
       </c>
-      <c r="C166" t="s">
+      <c r="D166" t="s">
         <v>1146</v>
-      </c>
-      <c r="D166" t="s">
-        <v>1147</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>367</v>
       </c>
       <c r="F166" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="G166" t="s">
         <v>1148</v>
       </c>
-      <c r="G166" t="s">
+      <c r="H166" s="2" t="s">
         <v>1149</v>
-      </c>
-      <c r="H166" s="2" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -11091,7 +12002,7 @@
         <v>343</v>
       </c>
       <c r="B167" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -11099,7 +12010,7 @@
         <v>344</v>
       </c>
       <c r="B168" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -11107,7 +12018,7 @@
         <v>345</v>
       </c>
       <c r="B169" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -11128,25 +12039,25 @@
         <v>348</v>
       </c>
       <c r="B172" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C172" s="2" t="s">
         <v>1154</v>
       </c>
-      <c r="C172" s="2" t="s">
+      <c r="D172" t="s">
         <v>1155</v>
       </c>
-      <c r="D172" t="s">
+      <c r="E172" t="s">
         <v>1156</v>
       </c>
-      <c r="E172" t="s">
+      <c r="F172" s="2" t="s">
         <v>1157</v>
       </c>
-      <c r="F172" s="2" t="s">
+      <c r="G172" s="2" t="s">
         <v>1158</v>
       </c>
-      <c r="G172" s="2" t="s">
+      <c r="H172" s="2" t="s">
         <v>1159</v>
-      </c>
-      <c r="H172" s="2" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -11154,7 +12065,7 @@
         <v>349</v>
       </c>
       <c r="B173" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -11162,10 +12073,10 @@
         <v>350</v>
       </c>
       <c r="B174" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C174" t="s">
         <v>1162</v>
-      </c>
-      <c r="C174" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="27">
@@ -11173,7 +12084,7 @@
         <v>351</v>
       </c>
       <c r="B175" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>369</v>
@@ -11184,7 +12095,7 @@
         <v>352</v>
       </c>
       <c r="B176" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="27">
@@ -11206,7 +12117,7 @@
         <v>372</v>
       </c>
       <c r="C178" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -11214,13 +12125,13 @@
         <v>355</v>
       </c>
       <c r="B179" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C179" t="s">
         <v>373</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E179" t="s">
         <v>374</v>
@@ -11236,13 +12147,13 @@
         <v>357</v>
       </c>
       <c r="B181" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C181" t="s">
         <v>1169</v>
       </c>
-      <c r="C181" t="s">
+      <c r="D181" t="s">
         <v>1170</v>
-      </c>
-      <c r="D181" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -11253,16 +12164,16 @@
         <v>375</v>
       </c>
       <c r="C182" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="D182" t="s">
         <v>376</v>
       </c>
       <c r="E182" t="s">
+        <v>1172</v>
+      </c>
+      <c r="F182" t="s">
         <v>1173</v>
-      </c>
-      <c r="F182" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -11270,10 +12181,10 @@
         <v>359</v>
       </c>
       <c r="B183" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C183" t="s">
         <v>1175</v>
-      </c>
-      <c r="C183" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -11286,10 +12197,10 @@
         <v>378</v>
       </c>
       <c r="B185" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C185" t="s">
         <v>1177</v>
-      </c>
-      <c r="C185" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -11308,10 +12219,10 @@
         <v>380</v>
       </c>
       <c r="B187" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C187" t="s">
         <v>1179</v>
-      </c>
-      <c r="C187" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -11319,19 +12230,19 @@
         <v>381</v>
       </c>
       <c r="B188" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C188" t="s">
         <v>1181</v>
       </c>
-      <c r="C188" t="s">
+      <c r="D188" t="s">
         <v>1182</v>
       </c>
-      <c r="D188" t="s">
+      <c r="E188" t="s">
         <v>1183</v>
       </c>
-      <c r="E188" t="s">
+      <c r="F188" t="s">
         <v>1184</v>
-      </c>
-      <c r="F188" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -11342,10 +12253,10 @@
         <v>411</v>
       </c>
       <c r="C189" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D189" t="s">
         <v>1186</v>
-      </c>
-      <c r="D189" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="40.5">
@@ -11353,13 +12264,13 @@
         <v>383</v>
       </c>
       <c r="B190" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>410</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="27">
@@ -11367,10 +12278,10 @@
         <v>384</v>
       </c>
       <c r="B191" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C191" s="2" t="s">
         <v>1190</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>1191</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -11378,13 +12289,13 @@
         <v>385</v>
       </c>
       <c r="B192" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C192" t="s">
         <v>412</v>
       </c>
       <c r="D192" t="s">
-        <v>1801</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="54">
@@ -11392,22 +12303,22 @@
         <v>386</v>
       </c>
       <c r="B193" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C193" t="s">
         <v>413</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>414</v>
       </c>
       <c r="F193" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="G193" s="2" t="s">
         <v>1195</v>
-      </c>
-      <c r="G193" s="2" t="s">
-        <v>1196</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -11415,10 +12326,10 @@
         <v>387</v>
       </c>
       <c r="B194" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C194" t="s">
         <v>1197</v>
-      </c>
-      <c r="C194" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -11426,7 +12337,7 @@
         <v>388</v>
       </c>
       <c r="B195" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="27">
@@ -11434,16 +12345,16 @@
         <v>389</v>
       </c>
       <c r="B196" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C196" s="2" t="s">
         <v>1200</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>1201</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>415</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>1802</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -11451,7 +12362,7 @@
         <v>390</v>
       </c>
       <c r="B197" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="198" spans="1:7" ht="27">
@@ -11459,10 +12370,10 @@
         <v>391</v>
       </c>
       <c r="B198" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C198" s="2" t="s">
         <v>1203</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -11470,7 +12381,7 @@
         <v>392</v>
       </c>
       <c r="B199" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="C199" t="s">
         <v>416</v>
@@ -11484,7 +12395,7 @@
         <v>393</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="C200" t="s">
         <v>418</v>
@@ -11495,10 +12406,10 @@
         <v>394</v>
       </c>
       <c r="B201" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C201" s="2" t="s">
         <v>1207</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>1208</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="27">
@@ -11506,16 +12417,16 @@
         <v>395</v>
       </c>
       <c r="B202" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C202" t="s">
         <v>1209</v>
-      </c>
-      <c r="C202" t="s">
-        <v>1210</v>
       </c>
       <c r="D202" t="s">
         <v>419</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -11523,7 +12434,7 @@
         <v>396</v>
       </c>
       <c r="B203" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -11531,13 +12442,13 @@
         <v>397</v>
       </c>
       <c r="B204" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C204" t="s">
         <v>1213</v>
       </c>
-      <c r="C204" t="s">
+      <c r="D204" t="s">
         <v>1214</v>
-      </c>
-      <c r="D204" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -11545,7 +12456,7 @@
         <v>398</v>
       </c>
       <c r="B205" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -11553,13 +12464,13 @@
         <v>399</v>
       </c>
       <c r="B206" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C206" s="2" t="s">
         <v>1217</v>
       </c>
-      <c r="C206" s="2" t="s">
+      <c r="D206" t="s">
         <v>1218</v>
-      </c>
-      <c r="D206" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -11567,7 +12478,7 @@
         <v>400</v>
       </c>
       <c r="B207" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -11578,13 +12489,13 @@
         <v>563</v>
       </c>
       <c r="C208" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D208" t="s">
         <v>1221</v>
       </c>
-      <c r="D208" t="s">
+      <c r="E208" t="s">
         <v>1222</v>
-      </c>
-      <c r="E208" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="209" spans="1:6" ht="27">
@@ -11592,10 +12503,10 @@
         <v>402</v>
       </c>
       <c r="B209" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C209" t="s">
         <v>1224</v>
-      </c>
-      <c r="C209" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -11603,10 +12514,10 @@
         <v>403</v>
       </c>
       <c r="B210" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C210" t="s">
         <v>1226</v>
-      </c>
-      <c r="C210" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="211" spans="1:6" ht="27">
@@ -11617,7 +12528,7 @@
         <v>564</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="212" spans="1:6" ht="27">
@@ -11625,10 +12536,10 @@
         <v>405</v>
       </c>
       <c r="B212" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C212" s="2" t="s">
         <v>1229</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="213" spans="1:6" ht="27">
@@ -11636,10 +12547,10 @@
         <v>406</v>
       </c>
       <c r="B213" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C213" s="2" t="s">
         <v>1231</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>1232</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>565</v>
@@ -11650,10 +12561,10 @@
         <v>407</v>
       </c>
       <c r="B214" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C214" t="s">
         <v>1233</v>
-      </c>
-      <c r="C214" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="215" spans="1:6" ht="27">
@@ -11677,7 +12588,7 @@
         <v>568</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="C217" t="s">
         <v>266</v>
@@ -11688,7 +12599,7 @@
         <v>569</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="219" spans="1:6" ht="27">
@@ -11696,13 +12607,13 @@
         <v>570</v>
       </c>
       <c r="B219" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C219" t="s">
         <v>1237</v>
       </c>
-      <c r="C219" t="s">
+      <c r="D219" t="s">
         <v>1238</v>
-      </c>
-      <c r="D219" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -11710,10 +12621,10 @@
         <v>571</v>
       </c>
       <c r="C220" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D220" s="2" t="s">
         <v>1240</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -11721,7 +12632,7 @@
         <v>572</v>
       </c>
       <c r="B221" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C221" t="s">
         <v>598</v>
@@ -11738,13 +12649,13 @@
         <v>599</v>
       </c>
       <c r="D222" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E222" s="2" t="s">
         <v>1243</v>
       </c>
-      <c r="E222" s="2" t="s">
+      <c r="F222" t="s">
         <v>1244</v>
-      </c>
-      <c r="F222" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -11755,10 +12666,10 @@
         <v>601</v>
       </c>
       <c r="C223" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D223" t="s">
         <v>1246</v>
-      </c>
-      <c r="D223" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -11766,7 +12677,7 @@
         <v>575</v>
       </c>
       <c r="B224" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="225" spans="1:6">
@@ -11774,7 +12685,7 @@
         <v>576</v>
       </c>
       <c r="B225" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -11782,7 +12693,7 @@
         <v>577</v>
       </c>
       <c r="B226" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -11811,19 +12722,19 @@
         <v>581</v>
       </c>
       <c r="B230" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C230" t="s">
         <v>1251</v>
       </c>
-      <c r="C230" t="s">
+      <c r="D230" t="s">
         <v>1252</v>
       </c>
-      <c r="D230" t="s">
+      <c r="E230" t="s">
         <v>1253</v>
       </c>
-      <c r="E230" t="s">
+      <c r="F230" t="s">
         <v>1254</v>
-      </c>
-      <c r="F230" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -11831,16 +12742,16 @@
         <v>582</v>
       </c>
       <c r="B231" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C231" t="s">
         <v>1256</v>
       </c>
-      <c r="C231" t="s">
+      <c r="D231" t="s">
         <v>1257</v>
       </c>
-      <c r="D231" t="s">
+      <c r="E231" t="s">
         <v>1258</v>
-      </c>
-      <c r="E231" t="s">
-        <v>1259</v>
       </c>
       <c r="F231" t="s">
         <v>603</v>
@@ -11851,10 +12762,10 @@
         <v>583</v>
       </c>
       <c r="B232" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C232" t="s">
         <v>1260</v>
-      </c>
-      <c r="C232" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="233" spans="1:6">
@@ -11862,7 +12773,7 @@
         <v>584</v>
       </c>
       <c r="B233" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -11870,7 +12781,7 @@
         <v>585</v>
       </c>
       <c r="B234" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -11878,16 +12789,16 @@
         <v>586</v>
       </c>
       <c r="B235" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C235" t="s">
         <v>1264</v>
       </c>
-      <c r="C235" t="s">
+      <c r="D235" t="s">
         <v>1265</v>
       </c>
-      <c r="D235" t="s">
+      <c r="E235" t="s">
         <v>1266</v>
-      </c>
-      <c r="E235" t="s">
-        <v>1267</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -11921,13 +12832,13 @@
         <v>591</v>
       </c>
       <c r="B240" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C240" t="s">
+        <v>1614</v>
+      </c>
+      <c r="D240" t="s">
         <v>1268</v>
-      </c>
-      <c r="C240" t="s">
-        <v>1617</v>
-      </c>
-      <c r="D240" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -11935,10 +12846,10 @@
         <v>592</v>
       </c>
       <c r="B241" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C241" t="s">
         <v>1270</v>
-      </c>
-      <c r="C241" t="s">
-        <v>1271</v>
       </c>
       <c r="D241" t="s">
         <v>606</v>
@@ -11949,16 +12860,16 @@
         <v>593</v>
       </c>
       <c r="B242" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="D242" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E242" s="2" t="s">
         <v>1274</v>
-      </c>
-      <c r="E242" s="2" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -11971,7 +12882,7 @@
         <v>595</v>
       </c>
       <c r="B244" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -11984,7 +12895,7 @@
         <v>607</v>
       </c>
       <c r="B246" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -11992,10 +12903,10 @@
         <v>608</v>
       </c>
       <c r="B247" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C247" t="s">
         <v>1277</v>
-      </c>
-      <c r="C247" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -12011,7 +12922,7 @@
         <v>610</v>
       </c>
       <c r="B249" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -12019,7 +12930,7 @@
         <v>611</v>
       </c>
       <c r="B250" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -12027,7 +12938,7 @@
         <v>612</v>
       </c>
       <c r="B251" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -12035,7 +12946,7 @@
         <v>613</v>
       </c>
       <c r="B252" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -12043,10 +12954,10 @@
         <v>614</v>
       </c>
       <c r="B253" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="C253" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -12054,7 +12965,7 @@
         <v>615</v>
       </c>
       <c r="B254" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -12062,7 +12973,7 @@
         <v>616</v>
       </c>
       <c r="B255" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -12078,7 +12989,7 @@
         <v>618</v>
       </c>
       <c r="B257" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -12094,7 +13005,7 @@
         <v>620</v>
       </c>
       <c r="B259" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -12102,7 +13013,7 @@
         <v>621</v>
       </c>
       <c r="B260" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -12110,13 +13021,13 @@
         <v>622</v>
       </c>
       <c r="B261" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C261" t="s">
         <v>1288</v>
       </c>
-      <c r="C261" t="s">
+      <c r="D261" t="s">
         <v>1289</v>
-      </c>
-      <c r="D261" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -12124,7 +13035,7 @@
         <v>623</v>
       </c>
       <c r="B262" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -12132,7 +13043,7 @@
         <v>624</v>
       </c>
       <c r="B263" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -12140,7 +13051,7 @@
         <v>625</v>
       </c>
       <c r="B264" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -12257,7 +13168,7 @@
         <v>672</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="E285" s="2"/>
       <c r="F285" s="2"/>
@@ -12273,16 +13184,16 @@
         <v>647</v>
       </c>
       <c r="B286" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C286" s="2" t="s">
         <v>1294</v>
       </c>
-      <c r="C286" s="2" t="s">
+      <c r="D286" s="2" t="s">
         <v>1295</v>
       </c>
-      <c r="D286" s="2" t="s">
+      <c r="E286" s="2" t="s">
         <v>1296</v>
-      </c>
-      <c r="E286" s="2" t="s">
-        <v>1297</v>
       </c>
       <c r="F286" s="2"/>
       <c r="G286" s="2"/>
@@ -12297,19 +13208,19 @@
         <v>648</v>
       </c>
       <c r="B287" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C287" s="2" t="s">
         <v>1298</v>
       </c>
-      <c r="C287" s="2" t="s">
+      <c r="D287" s="2" t="s">
         <v>1299</v>
       </c>
-      <c r="D287" s="2" t="s">
+      <c r="E287" s="2" t="s">
         <v>1300</v>
       </c>
-      <c r="E287" s="2" t="s">
+      <c r="F287" s="2" t="s">
         <v>1301</v>
-      </c>
-      <c r="F287" s="2" t="s">
-        <v>1302</v>
       </c>
       <c r="G287" s="2"/>
       <c r="H287" s="2"/>
@@ -12323,16 +13234,16 @@
         <v>649</v>
       </c>
       <c r="B288" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C288" s="2" t="s">
         <v>1303</v>
       </c>
-      <c r="C288" s="2" t="s">
+      <c r="D288" s="2" t="s">
         <v>1304</v>
       </c>
-      <c r="D288" s="2" t="s">
+      <c r="E288" s="2" t="s">
         <v>1305</v>
-      </c>
-      <c r="E288" s="2" t="s">
-        <v>1306</v>
       </c>
       <c r="F288" s="2"/>
       <c r="G288" s="2"/>
@@ -12353,7 +13264,7 @@
         <v>674</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="E289" s="2"/>
       <c r="F289" s="2"/>
@@ -12369,7 +13280,7 @@
         <v>651</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" s="2"/>
@@ -12393,10 +13304,10 @@
         <v>677</v>
       </c>
       <c r="D291" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E291" s="2" t="s">
         <v>1309</v>
-      </c>
-      <c r="E291" s="2" t="s">
-        <v>1310</v>
       </c>
       <c r="F291" s="2"/>
       <c r="G291" s="2"/>
@@ -12411,16 +13322,16 @@
         <v>653</v>
       </c>
       <c r="B292" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C292" s="2" t="s">
         <v>1311</v>
       </c>
-      <c r="C292" s="2" t="s">
+      <c r="D292" s="2" t="s">
         <v>1312</v>
       </c>
-      <c r="D292" s="2" t="s">
+      <c r="E292" s="2" t="s">
         <v>1313</v>
-      </c>
-      <c r="E292" s="2" t="s">
-        <v>1314</v>
       </c>
       <c r="F292" s="2"/>
       <c r="G292" s="2"/>
@@ -12487,7 +13398,7 @@
         <v>657</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" s="2"/>
@@ -12539,10 +13450,10 @@
         <v>660</v>
       </c>
       <c r="B299" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C299" s="2" t="s">
         <v>1316</v>
-      </c>
-      <c r="C299" s="2" t="s">
-        <v>1317</v>
       </c>
       <c r="D299" s="2"/>
       <c r="E299" s="2"/>
@@ -12559,13 +13470,13 @@
         <v>661</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>772</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>773</v>
@@ -12586,13 +13497,13 @@
         <v>773</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>774</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="F301" s="2"/>
       <c r="G301" s="2"/>
@@ -12625,7 +13536,7 @@
         <v>664</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="C303" s="2"/>
       <c r="D303" s="2"/>
@@ -12643,7 +13554,7 @@
         <v>665</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>930</v>
@@ -12663,10 +13574,10 @@
         <v>666</v>
       </c>
       <c r="B305" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C305" s="2" t="s">
         <v>1323</v>
-      </c>
-      <c r="C305" s="2" t="s">
-        <v>1324</v>
       </c>
       <c r="D305" s="2"/>
       <c r="E305" s="2"/>
@@ -12683,7 +13594,7 @@
         <v>667</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="C306" s="2"/>
       <c r="D306" s="2"/>
@@ -12701,13 +13612,13 @@
         <v>668</v>
       </c>
       <c r="B307" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C307" s="2" t="s">
         <v>1326</v>
       </c>
-      <c r="C307" s="2" t="s">
+      <c r="D307" s="2" t="s">
         <v>1327</v>
-      </c>
-      <c r="D307" s="2" t="s">
-        <v>1328</v>
       </c>
       <c r="E307" s="2"/>
       <c r="F307" s="2"/>
@@ -12744,13 +13655,13 @@
         <v>408</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>804</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="F309" s="2"/>
       <c r="G309" s="2"/>
@@ -12768,7 +13679,7 @@
         <v>805</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="D310" s="2" t="s">
         <v>806</v>
@@ -12787,7 +13698,7 @@
         <v>779</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>806</v>
@@ -12807,10 +13718,10 @@
         <v>780</v>
       </c>
       <c r="B312" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C312" s="2" t="s">
         <v>1333</v>
-      </c>
-      <c r="C312" s="2" t="s">
-        <v>1334</v>
       </c>
       <c r="D312" s="2"/>
       <c r="E312" s="2"/>
@@ -12830,13 +13741,13 @@
         <v>807</v>
       </c>
       <c r="C313" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D313" s="2" t="s">
         <v>1335</v>
       </c>
-      <c r="D313" s="2" t="s">
+      <c r="E313" s="2" t="s">
         <v>1336</v>
-      </c>
-      <c r="E313" s="2" t="s">
-        <v>1337</v>
       </c>
       <c r="F313" s="2"/>
       <c r="G313" s="2"/>
@@ -12854,7 +13765,7 @@
         <v>808</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="D314" s="2"/>
       <c r="E314" s="2"/>
@@ -12891,13 +13802,13 @@
         <v>784</v>
       </c>
       <c r="B316" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C316" s="2" t="s">
         <v>1339</v>
       </c>
-      <c r="C316" s="2" t="s">
+      <c r="D316" s="2" t="s">
         <v>1340</v>
-      </c>
-      <c r="D316" s="2" t="s">
-        <v>1341</v>
       </c>
       <c r="E316" s="2"/>
       <c r="F316" s="2"/>
@@ -12913,16 +13824,16 @@
         <v>785</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>1620</v>
+        <v>1617</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>810</v>
       </c>
       <c r="D317" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="E317" s="2" t="s">
         <v>1342</v>
-      </c>
-      <c r="E317" s="2" t="s">
-        <v>1343</v>
       </c>
       <c r="F317" s="2"/>
       <c r="G317" s="2"/>
@@ -12937,7 +13848,7 @@
         <v>786</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="C318" s="2"/>
       <c r="D318" s="2"/>
@@ -12973,13 +13884,13 @@
         <v>788</v>
       </c>
       <c r="B320" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C320" s="2" t="s">
         <v>1345</v>
       </c>
-      <c r="C320" s="2" t="s">
+      <c r="D320" s="2" t="s">
         <v>1346</v>
-      </c>
-      <c r="D320" s="2" t="s">
-        <v>1347</v>
       </c>
       <c r="E320" s="2"/>
       <c r="F320" s="2"/>
@@ -12995,7 +13906,7 @@
         <v>789</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C321" s="2"/>
       <c r="D321" s="2"/>
@@ -13036,7 +13947,7 @@
         <v>812</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="D323" s="2"/>
       <c r="E323" s="2"/>
@@ -13087,7 +13998,7 @@
         <v>794</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="C326" s="2"/>
       <c r="D326" s="2"/>
@@ -13105,10 +14016,10 @@
         <v>795</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>1809</v>
+        <v>1804</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D327" s="2"/>
       <c r="E327" s="2"/>
@@ -13125,7 +14036,7 @@
         <v>796</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="C328" s="2"/>
       <c r="D328" s="2"/>
@@ -13143,10 +14054,10 @@
         <v>797</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>1810</v>
+        <v>1805</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D329" s="2"/>
       <c r="E329" s="2"/>
@@ -13163,16 +14074,16 @@
         <v>798</v>
       </c>
       <c r="B330" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C330" s="2" t="s">
         <v>1355</v>
-      </c>
-      <c r="C330" s="2" t="s">
-        <v>1356</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>816</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="F330" s="2"/>
       <c r="G330" s="2"/>
@@ -13187,7 +14098,7 @@
         <v>799</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="C331" s="2"/>
       <c r="D331" s="2"/>
@@ -13208,7 +14119,7 @@
         <v>817</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D332" s="2"/>
       <c r="E332" s="2"/>
@@ -13225,13 +14136,13 @@
         <v>801</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>819</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E333" s="2" t="s">
         <v>818</v>
@@ -13249,7 +14160,7 @@
         <v>802</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="C334" s="2"/>
       <c r="D334" s="2"/>
@@ -13267,16 +14178,16 @@
         <v>803</v>
       </c>
       <c r="B335" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C335" s="2" t="s">
         <v>1362</v>
       </c>
-      <c r="C335" s="2" t="s">
+      <c r="D335" s="2" t="s">
         <v>1363</v>
       </c>
-      <c r="D335" s="2" t="s">
-        <v>1364</v>
-      </c>
       <c r="E335" s="2" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F335" s="2"/>
       <c r="G335" s="2"/>
@@ -13291,10 +14202,10 @@
         <v>820</v>
       </c>
       <c r="B336" s="2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C336" s="2" t="s">
         <v>1365</v>
-      </c>
-      <c r="C336" s="2" t="s">
-        <v>1366</v>
       </c>
       <c r="D336" s="2"/>
       <c r="E336" s="2"/>
@@ -13311,7 +14222,7 @@
         <v>821</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="C337" s="2"/>
       <c r="D337" s="2"/>
@@ -13332,7 +14243,7 @@
         <v>408</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D338" s="2"/>
       <c r="E338" s="2"/>
@@ -13349,10 +14260,10 @@
         <v>823</v>
       </c>
       <c r="B339" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C339" s="2" t="s">
         <v>1369</v>
-      </c>
-      <c r="C339" s="2" t="s">
-        <v>1370</v>
       </c>
       <c r="D339" s="2"/>
       <c r="E339" s="2"/>
@@ -13369,10 +14280,10 @@
         <v>824</v>
       </c>
       <c r="B340" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C340" s="2" t="s">
         <v>1371</v>
-      </c>
-      <c r="C340" s="2" t="s">
-        <v>1372</v>
       </c>
       <c r="D340" s="2"/>
       <c r="E340" s="2"/>
@@ -13389,13 +14300,13 @@
         <v>825</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>852</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="E341" s="2"/>
       <c r="F341" s="2"/>
@@ -13411,16 +14322,16 @@
         <v>826</v>
       </c>
       <c r="B342" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C342" s="2" t="s">
         <v>1374</v>
       </c>
-      <c r="C342" s="2" t="s">
+      <c r="D342" s="2" t="s">
         <v>1375</v>
       </c>
-      <c r="D342" s="2" t="s">
-        <v>1376</v>
-      </c>
       <c r="E342" s="2" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="F342" s="2"/>
       <c r="G342" s="2"/>
@@ -13435,7 +14346,7 @@
         <v>827</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="C343" s="2"/>
       <c r="D343" s="2"/>
@@ -13459,7 +14370,7 @@
         <v>856</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="E344" s="2"/>
       <c r="F344" s="2"/>
@@ -13475,7 +14386,7 @@
         <v>829</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
       <c r="C345" s="2"/>
       <c r="D345" s="2"/>
@@ -13511,10 +14422,10 @@
         <v>831</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="D347" s="2"/>
       <c r="E347" s="2"/>
@@ -13531,19 +14442,19 @@
         <v>832</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>853</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="E348" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="F348" s="2" t="s">
         <v>1379</v>
-      </c>
-      <c r="F348" s="2" t="s">
-        <v>1380</v>
       </c>
       <c r="G348" s="2"/>
       <c r="H348" s="2"/>
@@ -13557,10 +14468,10 @@
         <v>833</v>
       </c>
       <c r="B349" s="2" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C349" s="2" t="s">
         <v>1381</v>
-      </c>
-      <c r="C349" s="2" t="s">
-        <v>1382</v>
       </c>
       <c r="D349" s="2"/>
       <c r="E349" s="2"/>
@@ -13577,19 +14488,19 @@
         <v>834</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>912</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="E350" s="2" t="s">
         <v>913</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="G350" s="2"/>
       <c r="H350" s="2"/>
@@ -13603,7 +14514,7 @@
         <v>835</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="C351" s="2"/>
       <c r="D351" s="2"/>
@@ -13621,13 +14532,13 @@
         <v>836</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="C352" s="2" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D352" s="2" t="s">
         <v>1387</v>
-      </c>
-      <c r="D352" s="2" t="s">
-        <v>1388</v>
       </c>
       <c r="E352" s="2"/>
       <c r="F352" s="2"/>
@@ -13643,10 +14554,10 @@
         <v>837</v>
       </c>
       <c r="B353" s="2" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C353" s="2" t="s">
         <v>1389</v>
-      </c>
-      <c r="C353" s="2" t="s">
-        <v>1390</v>
       </c>
       <c r="D353" s="2"/>
       <c r="E353" s="2"/>
@@ -13668,22 +14579,22 @@
         <v>914</v>
       </c>
       <c r="C354" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D354" s="2" t="s">
         <v>1391</v>
       </c>
-      <c r="D354" s="2" t="s">
+      <c r="E354" s="2" t="s">
         <v>1392</v>
       </c>
-      <c r="E354" s="2" t="s">
+      <c r="F354" s="2" t="s">
         <v>1393</v>
       </c>
-      <c r="F354" s="2" t="s">
+      <c r="G354" s="2" t="s">
         <v>1394</v>
       </c>
-      <c r="G354" s="2" t="s">
+      <c r="H354" s="2" t="s">
         <v>1395</v>
-      </c>
-      <c r="H354" s="2" t="s">
-        <v>1396</v>
       </c>
       <c r="I354" s="2" t="s">
         <v>923</v>
@@ -13699,10 +14610,10 @@
         <v>838</v>
       </c>
       <c r="B355" s="2" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C355" s="2" t="s">
         <v>1397</v>
-      </c>
-      <c r="C355" s="2" t="s">
-        <v>1398</v>
       </c>
       <c r="D355" s="2" t="s">
         <v>925</v>
@@ -13723,16 +14634,16 @@
         <v>839</v>
       </c>
       <c r="B356" s="2" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C356" s="2" t="s">
         <v>1399</v>
       </c>
-      <c r="C356" s="2" t="s">
+      <c r="D356" s="2" t="s">
         <v>1400</v>
       </c>
-      <c r="D356" s="2" t="s">
+      <c r="E356" s="2" t="s">
         <v>1401</v>
-      </c>
-      <c r="E356" s="2" t="s">
-        <v>1402</v>
       </c>
       <c r="F356" s="2"/>
       <c r="G356" s="2"/>
@@ -13747,7 +14658,7 @@
         <v>840</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="C357" s="2"/>
       <c r="D357" s="2"/>
@@ -13765,16 +14676,16 @@
         <v>841</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>927</v>
       </c>
       <c r="D358" s="2" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E358" s="2" t="s">
         <v>1405</v>
-      </c>
-      <c r="E358" s="2" t="s">
-        <v>1406</v>
       </c>
       <c r="F358" s="2"/>
       <c r="G358" s="2"/>
@@ -13789,16 +14700,16 @@
         <v>842</v>
       </c>
       <c r="B359" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C359" s="2" t="s">
         <v>1407</v>
       </c>
-      <c r="C359" s="2" t="s">
+      <c r="D359" s="2" t="s">
         <v>1408</v>
       </c>
-      <c r="D359" s="2" t="s">
+      <c r="E359" s="2" t="s">
         <v>1409</v>
-      </c>
-      <c r="E359" s="2" t="s">
-        <v>1410</v>
       </c>
       <c r="F359" s="2"/>
       <c r="G359" s="2"/>
@@ -13813,22 +14724,22 @@
         <v>843</v>
       </c>
       <c r="B360" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C360" s="2" t="s">
         <v>1411</v>
       </c>
-      <c r="C360" s="2" t="s">
+      <c r="D360" s="2" t="s">
         <v>1412</v>
       </c>
-      <c r="D360" s="2" t="s">
+      <c r="E360" s="2" t="s">
         <v>1413</v>
-      </c>
-      <c r="E360" s="2" t="s">
-        <v>1414</v>
       </c>
       <c r="F360" s="2" t="s">
         <v>932</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H360" s="2"/>
       <c r="I360" s="2"/>
@@ -13841,25 +14752,25 @@
         <v>844</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>928</v>
       </c>
       <c r="D361" s="2" t="s">
+        <v>1416</v>
+      </c>
+      <c r="E361" s="2" t="s">
         <v>1417</v>
       </c>
-      <c r="E361" s="2" t="s">
+      <c r="F361" s="2" t="s">
         <v>1418</v>
-      </c>
-      <c r="F361" s="2" t="s">
-        <v>1419</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>929</v>
       </c>
       <c r="H361" s="2" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="I361" s="2"/>
       <c r="J361" s="2"/>
@@ -13871,22 +14782,22 @@
         <v>845</v>
       </c>
       <c r="B362" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C362" s="2" t="s">
         <v>1421</v>
       </c>
-      <c r="C362" s="2" t="s">
+      <c r="D362" s="2" t="s">
         <v>1422</v>
       </c>
-      <c r="D362" s="2" t="s">
+      <c r="E362" s="2" t="s">
         <v>1423</v>
       </c>
-      <c r="E362" s="2" t="s">
+      <c r="F362" s="2" t="s">
         <v>1424</v>
       </c>
-      <c r="F362" s="2" t="s">
+      <c r="G362" s="2" t="s">
         <v>1425</v>
-      </c>
-      <c r="G362" s="2" t="s">
-        <v>1426</v>
       </c>
       <c r="H362" s="2"/>
       <c r="I362" s="2"/>
@@ -13899,10 +14810,10 @@
         <v>846</v>
       </c>
       <c r="B363" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C363" s="2" t="s">
         <v>1427</v>
-      </c>
-      <c r="C363" s="2" t="s">
-        <v>1428</v>
       </c>
       <c r="D363" s="2"/>
       <c r="E363" s="2"/>
@@ -13935,7 +14846,7 @@
         <v>848</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C365" s="2"/>
       <c r="D365" s="2"/>
@@ -13953,16 +14864,16 @@
         <v>849</v>
       </c>
       <c r="B366" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C366" s="2" t="s">
         <v>1430</v>
-      </c>
-      <c r="C366" s="2" t="s">
-        <v>1431</v>
       </c>
       <c r="D366" s="2" t="s">
         <v>933</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="F366" s="2"/>
       <c r="G366" s="2"/>
@@ -13977,22 +14888,22 @@
         <v>850</v>
       </c>
       <c r="B367" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C367" s="2" t="s">
         <v>1433</v>
-      </c>
-      <c r="C367" s="2" t="s">
-        <v>1434</v>
       </c>
       <c r="D367" s="2" t="s">
         <v>934</v>
       </c>
       <c r="E367" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="F367" s="2" t="s">
         <v>1435</v>
       </c>
-      <c r="F367" s="2" t="s">
+      <c r="G367" s="2" t="s">
         <v>1436</v>
-      </c>
-      <c r="G367" s="2" t="s">
-        <v>1437</v>
       </c>
       <c r="H367" s="2"/>
       <c r="I367" s="2"/>
@@ -14005,10 +14916,10 @@
         <v>851</v>
       </c>
       <c r="B368" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="C368" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="D368" t="s">
         <v>935</v>
@@ -14080,7 +14991,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G297"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -14094,61 +15005,61 @@
     <col min="7" max="7" width="45.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="23.45" customHeight="1">
+    <row r="1" spans="1:7" ht="56.25" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>1557</v>
+        <v>1554</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>937</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1555</v>
+        <v>1896</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>938</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>989</v>
+        <v>1895</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="49.9" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>1558</v>
+        <v>1555</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>1460</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>1461</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>1462</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="4" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -14157,13 +15068,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="4" t="s">
-        <v>1560</v>
+        <v>1557</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1465</v>
+        <v>1894</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -14172,10 +15083,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="4" t="s">
-        <v>1561</v>
+        <v>1558</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -14185,10 +15096,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="4" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -14198,10 +15109,10 @@
     </row>
     <row r="7" spans="1:7" ht="27">
       <c r="A7" s="4" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -14211,49 +15122,51 @@
     </row>
     <row r="8" spans="1:7" ht="27">
       <c r="A8" s="4" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>1467</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>1469</v>
-      </c>
-      <c r="E8" s="4"/>
+      <c r="E8" s="4" t="s">
+        <v>1897</v>
+      </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="27">
       <c r="A9" s="4" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>1470</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>1471</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>1472</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="4" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -14262,10 +15175,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="4" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -14275,16 +15188,16 @@
     </row>
     <row r="12" spans="1:7" ht="27">
       <c r="A12" s="4" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>1476</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>1477</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>1478</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -14292,10 +15205,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="4" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -14305,13 +15218,13 @@
     </row>
     <row r="14" spans="1:7" ht="27">
       <c r="A14" s="4" t="s">
-        <v>1570</v>
+        <v>1567</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -14320,10 +15233,10 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="4" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -14333,10 +15246,10 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="4" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -14346,16 +15259,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="4" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>1482</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>1484</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>1485</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>1486</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
@@ -14363,10 +15276,10 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="4" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -14376,13 +15289,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="4" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -14391,13 +15304,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="4" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -14406,13 +15319,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="4" t="s">
-        <v>1577</v>
+        <v>1574</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -14421,10 +15334,10 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="4" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -14434,10 +15347,10 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="4" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -14447,10 +15360,10 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="4" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -14460,10 +15373,10 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="4" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -14473,10 +15386,10 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="4" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -14486,13 +15399,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="4" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -14501,10 +15414,10 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="4" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -14514,7 +15427,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="4" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -14525,10 +15438,10 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="4" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
@@ -14538,7 +15451,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="4" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -14549,7 +15462,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="4" t="s">
-        <v>1588</v>
+        <v>1585</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -14560,7 +15473,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="4" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -14571,7 +15484,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="4" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -14581,7 +15494,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="4" t="s">
-        <v>1591</v>
+        <v>1588</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>922</v>
@@ -14594,10 +15507,10 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="4" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -14607,10 +15520,10 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="4" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -14620,10 +15533,10 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="4" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -14633,10 +15546,10 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="4" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -14646,7 +15559,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="4" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -14657,7 +15570,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="4" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -14668,10 +15581,10 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="4" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1810</v>
+        <v>1805</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -14681,7 +15594,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="4" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -14692,10 +15605,10 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="4" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -14705,10 +15618,10 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="4" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
@@ -14718,7 +15631,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="4" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -14729,7 +15642,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="4" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -14740,7 +15653,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="4" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -14751,7 +15664,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="4" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -14762,7 +15675,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="4" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -14773,7 +15686,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="4" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -14784,7 +15697,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="4" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -14795,7 +15708,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="4" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>408</v>
@@ -14808,7 +15721,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="4" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -14819,7 +15732,7 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="4" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -14830,7 +15743,7 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="4" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -14841,7 +15754,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="4" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -14852,7 +15765,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="4" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -14863,7 +15776,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="4" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -17028,7 +17941,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -17230,7 +18143,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -18107,7 +19020,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A56"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -18117,282 +19030,282 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="26" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="26" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="26" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="26" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="26" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="26" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="26" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="26" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="26" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="26" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="26" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="26" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="26" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="26" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="26" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="26" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="26" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="26" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="26" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="26" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="26" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="26" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="26" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="26" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="26" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="26" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="26" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="26" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="26" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="26" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="26" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="26" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="26" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="26" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="26" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="26" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="26" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="26" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="26" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="26" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="26" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="26" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="26" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="26" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="26" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="26" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="26" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="26" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="26" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="26" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="26" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="26" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="26" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="26" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="26" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="26" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
     </row>
   </sheetData>
